--- a/MuestreoDeDatos_CastanoLiving.xlsx
+++ b/MuestreoDeDatos_CastanoLiving.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theal\Documents\Universidad\doo2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theal\OneDrive\Documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8003336-3DF0-4B54-9C98-7566944D28F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABC15A8-8962-4E35-8571-8D1AA3715D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="usuarios" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,13 @@
     <sheet name="clientes" sheetId="5" r:id="rId4"/>
     <sheet name="pedidos" sheetId="6" r:id="rId5"/>
     <sheet name="envios" sheetId="7" r:id="rId6"/>
-    <sheet name="pedido_items" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="67">
   <si>
     <t>id</t>
   </si>
@@ -73,21 +72,9 @@
     <t>disponible</t>
   </si>
   <si>
-    <t>Silla Venecia</t>
-  </si>
-  <si>
-    <t>Silla Roma</t>
-  </si>
-  <si>
     <t>Comedor 4 puestos Roble</t>
   </si>
   <si>
-    <t>Mesa de trabajo Roble</t>
-  </si>
-  <si>
-    <t>Mesa de centro Venecia</t>
-  </si>
-  <si>
     <t>ciudad</t>
   </si>
   <si>
@@ -97,12 +84,6 @@
     <t>Medellín</t>
   </si>
   <si>
-    <t>producto_id</t>
-  </si>
-  <si>
-    <t>cantidad</t>
-  </si>
-  <si>
     <t>telefono</t>
   </si>
   <si>
@@ -212,12 +193,6 @@
   </si>
   <si>
     <t>EN-99201</t>
-  </si>
-  <si>
-    <t>nombre_producto</t>
-  </si>
-  <si>
-    <t>precio_unitario</t>
   </si>
   <si>
     <t>Vendedor</t>
@@ -326,14 +301,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,23 +612,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -673,7 +648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -689,16 +664,16 @@
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>46174</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -709,7 +684,7 @@
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <v>46174</v>
       </c>
     </row>
@@ -724,20 +699,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,70 +726,70 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="6">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4">
         <v>1450</v>
       </c>
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="6">
+        <v>58</v>
+      </c>
+      <c r="C5" s="4">
         <v>1650</v>
       </c>
       <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="6">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4">
         <v>1200</v>
       </c>
       <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="6">
+        <v>59</v>
+      </c>
+      <c r="C7" s="4">
         <v>1550</v>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="6">
+        <v>60</v>
+      </c>
+      <c r="C8" s="4">
         <v>2250</v>
       </c>
       <c r="D8" s="2" t="b">
@@ -832,17 +807,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -850,18 +827,18 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -875,17 +852,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -893,40 +872,40 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2">
         <v>3135526916</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2">
         <v>3052392681</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -940,10 +919,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="23.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
@@ -951,51 +930,51 @@
     <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+    </row>
+    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1009,23 +988,23 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2">
         <v>770</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="3">
         <v>46183</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1040,22 +1019,22 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H5" s="2">
         <v>1200</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="3">
         <v>46184</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1069,20 +1048,20 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2">
         <v>810</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="3">
         <v>46185</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1096,77 +1075,77 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="26.9296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="3" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1177,22 +1156,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1203,19 +1182,19 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1224,150 +1203,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2">
-        <v>210</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="2">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>31</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="2">
-        <v>350</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="2">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1200</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="2">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2">
-        <v>180</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="2">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2">
-        <v>21</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2">
-        <v>450</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>